--- a/quality_data.xlsx
+++ b/quality_data.xlsx
@@ -5,18 +5,21 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\one-or-few-shot-3d-reconstruction\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Studia\Dyplomowanie\recon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D5D82F-01F9-4D70-98BE-AB22ECDDB9D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A120E6-B09D-4A6B-AFA8-0F4151F68823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ocena" sheetId="2" r:id="rId1"/>
     <sheet name="Skala" sheetId="3" r:id="rId2"/>
     <sheet name="Podsumowanie" sheetId="4" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Ocena!$A$1:$R$419</definedName>
+  </definedNames>
   <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -2317,11 +2320,11 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5895,7 +5898,7 @@
         <v>94</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F57" s="10">
         <v>1</v>
@@ -5952,7 +5955,7 @@
         <v>94</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F58" s="10">
         <v>1</v>
@@ -6009,7 +6012,7 @@
         <v>94</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F59" s="10">
         <v>2</v>
@@ -6066,7 +6069,7 @@
         <v>94</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F60" s="10">
         <v>2</v>
@@ -6123,7 +6126,7 @@
         <v>94</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F61" s="10">
         <v>2</v>
@@ -6180,7 +6183,7 @@
         <v>94</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F62" s="10">
         <v>4</v>
@@ -6237,7 +6240,7 @@
         <v>94</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F63" s="10">
         <v>4</v>
@@ -6294,7 +6297,7 @@
         <v>94</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F64" s="10">
         <v>4</v>
@@ -6351,7 +6354,7 @@
         <v>94</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F65" s="10">
         <v>8</v>
@@ -6408,7 +6411,7 @@
         <v>94</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F66" s="10">
         <v>8</v>
@@ -6465,7 +6468,7 @@
         <v>94</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F67" s="10">
         <v>8</v>
@@ -6522,7 +6525,7 @@
         <v>107</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F68" s="10">
         <v>1</v>
@@ -6579,7 +6582,7 @@
         <v>107</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F69" s="10">
         <v>1</v>
@@ -6636,7 +6639,7 @@
         <v>107</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F70" s="10">
         <v>2</v>
@@ -6693,7 +6696,7 @@
         <v>107</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F71" s="10">
         <v>2</v>
@@ -6750,7 +6753,7 @@
         <v>107</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F72" s="10">
         <v>2</v>
@@ -6807,7 +6810,7 @@
         <v>107</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F73" s="10">
         <v>4</v>
@@ -6864,7 +6867,7 @@
         <v>107</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F74" s="10">
         <v>4</v>
@@ -6921,7 +6924,7 @@
         <v>107</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F75" s="10">
         <v>4</v>
@@ -6978,7 +6981,7 @@
         <v>107</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F76" s="10">
         <v>8</v>
@@ -7035,7 +7038,7 @@
         <v>107</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F77" s="10">
         <v>8</v>
@@ -7092,7 +7095,7 @@
         <v>107</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F78" s="10">
         <v>8</v>
@@ -26626,13 +26629,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>524</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
     </row>
     <row r="2" spans="1:5" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -26720,34 +26723,34 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="16" t="s">
         <v>549</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
     </row>
     <row r="8" spans="1:5" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
     </row>
     <row r="9" spans="1:5" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
     </row>
     <row r="10" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -26778,28 +26781,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>550</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
-      <c r="S1" s="16"/>
-      <c r="T1" s="16"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
     </row>
     <row r="2" spans="1:20" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
